--- a/plots/data.xlsx
+++ b/plots/data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,49 +510,199 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02855332</v>
+        <v>0.009559701</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01430169</v>
+        <v>0.00477855</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01425164</v>
+        <v>0.004781151</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.005005291</v>
+        <v>0.0002600743</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.002500067</v>
+        <v>9.47976e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.002505224</v>
+        <v>0.0001652767</v>
       </c>
       <c r="H2" t="n">
-        <v>2.578343e-06</v>
+        <v>-3.523955e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>2.502645e-05</v>
+        <v>-1.300372e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0001427666</v>
+        <v>4.77985e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>3.052445e-21</v>
+        <v>5.401883e-22</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001427666</v>
+        <v>4.77985e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0001427666</v>
+        <v>-4.77985e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>37.81135</v>
+        <v>34.43546</v>
       </c>
       <c r="O2" t="n">
-        <v>41.99451</v>
+        <v>41.19444</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.0108204</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.002936633</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.00788377</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.4947137</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2605284</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.2341853</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.01317155</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-0.002473568</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5.410201e-05</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.545342e-19</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5.410201e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-5.410201e-05</v>
+      </c>
+      <c r="N3" t="n">
+        <v>34.26422</v>
+      </c>
+      <c r="O3" t="n">
+        <v>74.22896</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.01521334</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.002723706</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.01248963</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9765925</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5132498</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.4633427</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.02495355</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-0.004882963</v>
+      </c>
+      <c r="J4" t="n">
+        <v>7.606668999999999e-05</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.851391e-19</v>
+      </c>
+      <c r="L4" t="n">
+        <v>7.606668999999999e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-7.606668999999999e-05</v>
+      </c>
+      <c r="N4" t="n">
+        <v>33.41086</v>
+      </c>
+      <c r="O4" t="n">
+        <v>112.7876</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.02724348</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.006839899</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.02040358</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.356368</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.7182955</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.6380728</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.04011136</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0.006781841</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.0001362174</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.801647999999999e-19</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0001362174</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-0.0001362174</v>
+      </c>
+      <c r="N5" t="n">
+        <v>30.81951</v>
+      </c>
+      <c r="O5" t="n">
+        <v>147.8917</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
